--- a/QCM2_1_CH.xlsx
+++ b/QCM2_1_CH.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\WEB_TEST_APP\MED-CONTEST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61979F43-C721-4383-9ABB-860AD6757C90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA5BE97E-C64B-41D2-87C5-860411FBBB8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -63,527 +63,532 @@
     <t>OptionE</t>
   </si>
   <si>
-    <t>Identifier les deux couples rédox mis en jeu dans cette réaction d'oxydoréduction :
+    <t>La vitesse de réaction à un instant donné :</t>
+  </si>
+  <si>
+    <t>La vitesse de réaction au cours de cette transformation :</t>
+  </si>
+  <si>
+    <t>L'état final d'un système est atteint à un instant $t_f$. La vitesse de réaction pour ce système est maximale :</t>
+  </si>
+  <si>
+    <t>L'étude cinétique a été réalisée dans un volume V = 100 mL d'une solution d'urée de concentration C = 0,020 mol/L. L'avancement maximal est :</t>
+  </si>
+  <si>
+    <t>L'avancement à la date $t = 3.t_{1/2}$ est :</t>
+  </si>
+  <si>
+    <t>A $t = t_{1/2}$ le taux d'avancement de la réaction est :</t>
+  </si>
+  <si>
+    <t>A la fin de la réaction,</t>
+  </si>
+  <si>
+    <t>Le temps de demi-réaction est égal à :</t>
+  </si>
+  <si>
+    <t>La concentration $c'$ du méthanol peut s'écrire :</t>
+  </si>
+  <si>
+    <t>La quantité de dihydrogène formé est égale :</t>
+  </si>
+  <si>
+    <t>Le volume de gaz dégagé dans l'enceinte est égal à 2,5 L.</t>
+  </si>
+  <si>
+    <t>A la fin de la transformation il reste au fond de l'erlenmeyer :</t>
+  </si>
+  <si>
+    <t>Peroxyde d'hydrogène : Soit l'oxydation en milieu acide du peroxyde d'hydrogène par les ions iodures en excès. On peut exprimer la vitesse volumique de réaction $v$ :</t>
+  </si>
+  <si>
+    <t>La variation temporelle de $[I^{-}_{(aq)}]$ est de la forme (courbe décroissante) :</t>
+  </si>
+  <si>
+    <t>A l'état final, la pression dans l'enceinte est égale à :</t>
+  </si>
+  <si>
+    <t>L'expression de la pression dans l'enceinte à un instant t est :</t>
+  </si>
+  <si>
+    <t>Au bout de dix secondes, l'avancement est :</t>
+  </si>
+  <si>
+    <t>L'oxydation dans une enceinte fermée, la réaction du dioxyde de soufre $SO_2$ sur le dioxygène $O_2$ donne du trioxyde de soufre $SO_3$.</t>
+  </si>
+  <si>
+    <t>Ion peroxodisulfate et ion iodure : $S_2O_8^{2-} + 2I^- \rightarrow I_2 + 2SO_4^{2-}$. V=100 mL, C1=0.40 mol/L et C2=0.36 mol/L.</t>
+  </si>
+  <si>
+    <t>Etude de la réaction $aA + bB \rightarrow ...$ Au temps $t = 0$, la concentration $c_{0(A)}$ est égale à :</t>
+  </si>
+  <si>
+    <t>Au temps $t_{1/2}$ :</t>
+  </si>
+  <si>
+    <t>Le temps de demi-réaction est compris entre :</t>
+  </si>
+  <si>
+    <t>La courbe 1 correspond au :</t>
+  </si>
+  <si>
+    <t>Si $a = 1$ alors :</t>
+  </si>
+  <si>
+    <t>Si on dilue le mélange réactionnel, les asymptotes horizontales aux courbes 1 et 2 sont plus élevées sur le graphe.</t>
+  </si>
+  <si>
+    <t>$Zn^{2+}_{(aq)} / Zn_{(s)}$ et $H_{3}O^{+}_{(aq)} / H_{2(g)}$</t>
+  </si>
+  <si>
+    <t>$Zn^{2+}_{(aq)} / Zn_{(s)}$ et $H_{3}O^{+}_{(aq)} / H_{2}O_{(l)}$</t>
+  </si>
+  <si>
+    <t>$H_{3}O^{+}_{(aq)} / H_{2(g)}$ et $Zn_{(s)} / Zn^{2+}_{(aq)}$</t>
+  </si>
+  <si>
+    <t>$H_{3}O^{+}_{(aq)} / H_{2}O_{(l)}$ et $Zn_{(s)} / Zn^{2+}_{(aq)}$</t>
+  </si>
+  <si>
+    <t>$H_{2}O_{2(aq)} / O_{2(g)}$ et $H_{2}O_{2(aq)} / H_{2}O_{(l)}$</t>
+  </si>
+  <si>
+    <t>$H_{2}O_{2(aq)} / O_{2(g)}$ et $O_{2(g)} / H_{2}O_{2(aq)}$</t>
+  </si>
+  <si>
+    <t>$O_{2(g)} / H_{2}O_{2(aq)}$ et $H_{2}O_{2(aq)} / H_{2}O_{(l)}$</t>
+  </si>
+  <si>
+    <t>$H_{2}O / H_{2}O_{2(aq)}$ et $O_{2(g)} / H_{2}O_{2(aq)}$</t>
+  </si>
+  <si>
+    <t>$MnO_{4(aq)}^{-} / Mn^{2+}_{(aq)}$ et $Fe^{3+}_{(aq)} / Fe^{2+}_{(aq)}$</t>
+  </si>
+  <si>
+    <t>$MnO_{4(aq)}^{-} / Mn^{2+}_{(aq)}$ et $H^{+}_{(aq)} / H_{2}O_{(l)}$</t>
+  </si>
+  <si>
+    <t>$Mn^{2+}_{(aq)} / MnO_{4(aq)}^{-}$ et $Fe^{2+}_{(aq)} / Fe^{3+}_{(aq)}$</t>
+  </si>
+  <si>
+    <t>Autre réponse</t>
+  </si>
+  <si>
+    <t>$Al_{(s)} / AlO_{2(aq)}^{-}$ et $HO^{-}_{(aq)} / H_{2(g)}$</t>
+  </si>
+  <si>
+    <t>$AlO_{2(aq)}^{-} / Al_{(s)}$ et $HO^{-}_{(aq)} / H_{2(g)}$</t>
+  </si>
+  <si>
+    <t>$AlO_{2(aq)}^{-} / Al_{(s)}$ et $HO^{-}_{(aq)} / H_{2}O_{(l)}$</t>
+  </si>
+  <si>
+    <t>$AlO_{2(aq)}^{-} / Al_{(s)}$ et $H_{2}O_{(l)} / HO^{-}_{(aq)}$</t>
+  </si>
+  <si>
+    <t>$Cl_{2(g)} / Cl^{-}_{(aq)}$ et $HO^{-}_{(aq)} / H_{2}O_{(l)}$</t>
+  </si>
+  <si>
+    <t>$Cl_{2(g)} / Cl^{-}_{(aq)}$ et $H_{2}O_{(l)} / HO^{-}_{(aq)}$</t>
+  </si>
+  <si>
+    <t>$Cl_{2(g)} / Cl^{-}_{(aq)}$ et $Cl_{2(g)} / ClO^{-}_{(aq)}$</t>
+  </si>
+  <si>
+    <t>$Cl_{2(g)} / Cl^{-}_{(aq)}$ et $ClO^{-}_{(aq)} / Cl_{2(g)}$</t>
+  </si>
+  <si>
+    <t>$H_{2}O_{2(aq)} / H_{2}O_{(l)}$ et $I_{2(g)} / I^{-}_{(aq)}$</t>
+  </si>
+  <si>
+    <t>$H_{2}O_{2(aq)} / H_{2}O_{(l)}$ et $I^{-}_{(aq)} / I_{2(g)}$</t>
+  </si>
+  <si>
+    <t>$H_{2}O_{(l)} / H_{2}O_{2(aq)}$ et $I_{2(g)} / I^{-}_{(aq)}$</t>
+  </si>
+  <si>
+    <t>$H_{2}O / H_{2}O_{2(aq)}$ et $I^{-}_{(aq)} / I_{2(g)}$</t>
+  </si>
+  <si>
+    <t>$S_{2}O_{8(aq)}^{2-} / SO_{4(aq)}^{2-}$ et $I^{-}_{(aq)} / I_{2(aq)}$</t>
+  </si>
+  <si>
+    <t>$S_{2}O_{8(aq)}^{2-} / SO_{4(aq)}^{2-}$ et $I_{2(g)} / I^{-}_{(aq)}$</t>
+  </si>
+  <si>
+    <t>$SO_{4(aq)}^{2-} / S_{2}O_{8(aq)}^{2-}$ et $I^{-}_{(aq)} / I_{2(g)}$</t>
+  </si>
+  <si>
+    <t>$SO_{4(aq)}^{2-} / S_{2}O_{8(aq)}^{2-}$ et $I_{2(g)} / I^{-}_{(aq)}$</t>
+  </si>
+  <si>
+    <t>$Cl_{2(g)} / Cl^{-}_{(aq)}$ et $I_{2(g)} / I^{-}_{(aq)}$</t>
+  </si>
+  <si>
+    <t>$Cl^{-}_{(aq)} / Cl_{2(g)}$ et $I^{-}_{(aq)} / I_{2(g)}$</t>
+  </si>
+  <si>
+    <t>$Cl_{2(g)} / Cl^{-}_{(aq)}$ et $ICl_{3(s)} / I_{2(g)}$</t>
+  </si>
+  <si>
+    <t>$Cl_{2(g)} / Cl^{-}_{(aq)}$ et $I_{2(g)} / ICl_{3(s)}$</t>
+  </si>
+  <si>
+    <t>$V = \frac{1}{2}\frac{d[I_2]}{dt}$</t>
+  </si>
+  <si>
+    <t>$V = - \frac{d[I_2]}{dt}$</t>
+  </si>
+  <si>
+    <t>$V = \frac{d[I_2]}{dt}$</t>
+  </si>
+  <si>
+    <t>$V = \frac{1}{V_1 + V_2}\frac{d[I_2]}{dt}$</t>
+  </si>
+  <si>
+    <t>Dépend de la couleur des espèces chimiques qui constituent le système</t>
+  </si>
+  <si>
+    <t>Dépend du volume du mélange réactionnel</t>
+  </si>
+  <si>
+    <t>Dépend de la concentration des produits</t>
+  </si>
+  <si>
+    <t>Dépend de la température</t>
+  </si>
+  <si>
+    <t>Augmente avec le temps</t>
+  </si>
+  <si>
+    <t>Diminue avec le temps</t>
+  </si>
+  <si>
+    <t>Augmente puis diminue</t>
+  </si>
+  <si>
+    <t>Ne varie pas</t>
+  </si>
+  <si>
+    <t>à l'instant $t_f$</t>
+  </si>
+  <si>
+    <t>à l'instant $t = 0$</t>
+  </si>
+  <si>
+    <t>à l'instant $t_{1/2}$</t>
+  </si>
+  <si>
+    <t>à l'instant $t = \infty$</t>
+  </si>
+  <si>
+    <t>$v = \frac{d[(NH_2)_2CO]}{dt}$</t>
+  </si>
+  <si>
+    <t>$v = -\frac{d[(NH_2)_2CO]}{dt}$</t>
+  </si>
+  <si>
+    <t>$v = \frac{1}{V}\frac{d[(NH_2)_2CO]}{dt}$</t>
+  </si>
+  <si>
+    <t>$v = -\frac{1}{V}\frac{d[(NH_2)_2CO]}{dt}$</t>
+  </si>
+  <si>
+    <t>$x_{max} = 1,0~mmol$</t>
+  </si>
+  <si>
+    <t>$x_{max} = 1,7~mmol$</t>
+  </si>
+  <si>
+    <t>$x_{max} = 2,0~mmol$</t>
+  </si>
+  <si>
+    <t>$x_{max} = 4,0~mmol$</t>
+  </si>
+  <si>
+    <t>$x(3t_{1/2}) = 1,35~mmol$</t>
+  </si>
+  <si>
+    <t>$x(3t_{1/2}) = 1,55~mmol$</t>
+  </si>
+  <si>
+    <t>$x(3t_{1/2}) = 1,75~mmol$</t>
+  </si>
+  <si>
+    <t>$x(3t_{1/2}) = 2,0~mmol$</t>
+  </si>
+  <si>
+    <t>40%</t>
+  </si>
+  <si>
+    <t>50%</t>
+  </si>
+  <si>
+    <t>60%</t>
+  </si>
+  <si>
+    <t>80%</t>
+  </si>
+  <si>
+    <t>$a = 0$</t>
+  </si>
+  <si>
+    <t>$a = 1$</t>
+  </si>
+  <si>
+    <t>$a = -1$</t>
+  </si>
+  <si>
+    <t>il reste encore d'iodure de méthyle dans le milieu réactionnel.</t>
+  </si>
+  <si>
+    <t>il ne reste plus d'iodure de méthyle dans le milieu réactionnel.</t>
+  </si>
+  <si>
+    <t>l'iodure de méthyle est une espèce spectatrice.</t>
+  </si>
+  <si>
+    <t>$t_{1/2} = a$</t>
+  </si>
+  <si>
+    <t>$t_{1/2} = b$</t>
+  </si>
+  <si>
+    <t>$t_{1/2} = 1/b$</t>
+  </si>
+  <si>
+    <t>$t_{1/2} = -b$</t>
+  </si>
+  <si>
+    <t>$c' = c_0 \frac{bt}{1 - bt}$</t>
+  </si>
+  <si>
+    <t>$c' = c_0 \frac{1 + bt}{bt}$</t>
+  </si>
+  <si>
+    <t>$c' = c_0 \frac{bt}{1 + bt}$</t>
+  </si>
+  <si>
+    <t>$c' = c_0 \frac{1 - bt}{bt}$</t>
+  </si>
+  <si>
+    <t>Vrai</t>
+  </si>
+  <si>
+    <t>Faux</t>
+  </si>
+  <si>
+    <t>$n(H_2) = 0,05~mol$</t>
+  </si>
+  <si>
+    <t>$n(H_2) = 0,06~mol$</t>
+  </si>
+  <si>
+    <t>$n(H_2) = 0,08~mol$</t>
+  </si>
+  <si>
+    <t>$n(H_2) = 0,1~mol$</t>
+  </si>
+  <si>
+    <t>$V = 2,5~L$</t>
+  </si>
+  <si>
+    <t>$V = 4~L$</t>
+  </si>
+  <si>
+    <t>$V = 5~L$</t>
+  </si>
+  <si>
+    <t>$V = 8~L$</t>
+  </si>
+  <si>
+    <t>moins de la moitié de la quantité de matière initiale de zinc.</t>
+  </si>
+  <si>
+    <t>la moitié de la quantité de matière initiale de zinc.</t>
+  </si>
+  <si>
+    <t>plus de la moitié de la quantité de matière initiale de zinc.</t>
+  </si>
+  <si>
+    <t>Le zinc est en défaut.</t>
+  </si>
+  <si>
+    <t>Comme la dérivée temporelle de l'avancement x.</t>
+  </si>
+  <si>
+    <t>Comme la dérivée volumique de l'avancement x.</t>
+  </si>
+  <si>
+    <t>En divisant la pente de la tangente à l'origine de la courbe $x(t)$ par le volume.</t>
+  </si>
+  <si>
+    <t>$P_0$</t>
+  </si>
+  <si>
+    <t>$2P_0$</t>
+  </si>
+  <si>
+    <t>$3P_0$</t>
+  </si>
+  <si>
+    <t>Autre</t>
+  </si>
+  <si>
+    <t>$4P_0$</t>
+  </si>
+  <si>
+    <t>$P = P_0 + \frac{x(t)RT}{V}$</t>
+  </si>
+  <si>
+    <t>$P = P_0 + \frac{2x(t)RT}{V}$</t>
+  </si>
+  <si>
+    <t>$P = P_0 + \frac{3x(t)RT}{V}$</t>
+  </si>
+  <si>
+    <t>$P = P_0 + \frac{4x(t)RT}{V}$</t>
+  </si>
+  <si>
+    <t>$x = 0,0125~mol$</t>
+  </si>
+  <si>
+    <t>$x = 0,125~mol$</t>
+  </si>
+  <si>
+    <t>$x = 1,25~mol$</t>
+  </si>
+  <si>
+    <t>Le mélange est réalisé dans des conditions stœchiométriques.</t>
+  </si>
+  <si>
+    <t>La quantité maximale de trioxyde de soufre formé est 20 mmol.</t>
+  </si>
+  <si>
+    <t>Le temps de demi-réaction est $t_{1/2} = 30~s$.</t>
+  </si>
+  <si>
+    <t>La courbe 3 représente l'évolution de la quantité de dioxygène au cours du temps.</t>
+  </si>
+  <si>
+    <t>Le réactif limitant est l'ion iodure.</t>
+  </si>
+  <si>
+    <t>La réaction est finie à $t &gt; 50~min$.</t>
+  </si>
+  <si>
+    <t>La vitesse volumique molaire est proportionnelle au volume.</t>
+  </si>
+  <si>
+    <t>Cette vitesse est d'abord positive, s'annule puis est négative.</t>
+  </si>
+  <si>
+    <t>$\frac{C_0}{5}$</t>
+  </si>
+  <si>
+    <t>$\frac{4C_0}{5}$</t>
+  </si>
+  <si>
+    <t>$\frac{C_{0(B)}}{4}$</t>
+  </si>
+  <si>
+    <t>$\frac{4C_{0(B)}}{5}$</t>
+  </si>
+  <si>
+    <t>50% d'un des réactifs a disparu.</t>
+  </si>
+  <si>
+    <t>25% d'un des réactifs a disparu.</t>
+  </si>
+  <si>
+    <t>75% d'un des réactifs a disparu.</t>
+  </si>
+  <si>
+    <t>2 et 3 heures.</t>
+  </si>
+  <si>
+    <t>3 et 4 heures.</t>
+  </si>
+  <si>
+    <t>4 et 5 heures.</t>
+  </si>
+  <si>
+    <t>5 et 6 heures.</t>
+  </si>
+  <si>
+    <t>réactif A.</t>
+  </si>
+  <si>
+    <t>réactif B.</t>
+  </si>
+  <si>
+    <t>$b = 0$</t>
+  </si>
+  <si>
+    <t>$b = a$</t>
+  </si>
+  <si>
+    <t>$b = 2a$</t>
+  </si>
+  <si>
+    <t>$b = 8a$</t>
+  </si>
+  <si>
+    <t>CHIMIE CINETIQUE</t>
+  </si>
+  <si>
+    <t>Identifier les deux couples rédox mis en jeu dans cette réaction d'oxydoréduction :&lt;br&gt;
 $Zn_{(s)} + 2H_{3}O^{+}_{(aq)} \rightarrow Zn^{2+}_{(aq)} + H_{2(g)} + 2H_{2}O_{(l)}$</t>
   </si>
   <si>
-    <t>Identifier les deux couples rédox mis en jeu dans cette réaction d'oxydoréduction :
+    <t>Identifier les deux couples rédox mis en jeu dans cette réaction d'oxydoréduction :&lt;br&gt;
 $2H_{2}O_{2(aq)} \rightarrow O_{2(g)} + 2H_{2}O_{(l)}$</t>
   </si>
   <si>
-    <t>Identifier les deux couples rédox mis en jeu dans cette réaction d'oxydoréduction :
+    <t>Identifier les deux couples rédox mis en jeu dans cette réaction d'oxydoréduction :&lt;br&gt;
 $MnO_{4(aq)}^{-} + 8H^{+}_{(aq)} + 5Fe^{2+}_{(aq)} \rightarrow Mn^{2+}_{(aq)} + 5Fe^{3+}_{(aq)} + 4H_{2}O_{(l)}$</t>
   </si>
   <si>
-    <t>Identifier les deux couples rédox mis en jeu dans cette réaction d'oxydoréduction :
+    <t>Identifier les deux couples rédox mis en jeu dans cette réaction d'oxydoréduction :&lt;br&gt;
 $2Al_{(s)} + 2HO^{-}_{(aq)} + 2H_{2}O_{(l)} \rightarrow 2AlO_{2(aq)}^{-} + 3H_{2(g)}$</t>
   </si>
   <si>
-    <t>Identifier les deux couples rédox mis en jeu dans cette réaction d'oxydoréduction :
+    <t>Identifier les deux couples rédox mis en jeu dans cette réaction d'oxydoréduction :&lt;br&gt;
 $Cl_{2(g)} + 2HO^{-}_{(aq)} \rightarrow Cl^{-}_{(aq)} + ClO^{-}_{(aq)} + H_{2}O_{(l)}$</t>
   </si>
   <si>
-    <t>Identifier les deux couples rédox mis en jeu dans cette réaction d'oxydoréduction :
+    <t>Identifier les deux couples rédox mis en jeu dans cette réaction d'oxydoréduction :&lt;br&gt;
 $H_{2}O_{2(aq)} + 2I^{-}_{(aq)} + 2H^{+}_{(aq)} \rightarrow 2H_{2}O_{(l)} + I_{2(aq)}$</t>
   </si>
   <si>
-    <t>Identifier les deux couples rédox mis en jeu dans cette réaction d'oxydoréduction :
+    <t>Identifier les deux couples rédox mis en jeu dans cette réaction d'oxydoréduction :&lt;br&gt;
 $S_{2}O_{8(aq)}^{2-} + 2I^{-}_{(aq)} \rightarrow 2SO_{4(aq)}^{2-} + I_{2(aq)}$</t>
   </si>
   <si>
-    <t>Identifier les deux couples rédox mis en jeu dans cette réaction d'oxydoréduction :
+    <t>Identifier les deux couples rédox mis en jeu dans cette réaction d'oxydoréduction :&lt;br&gt;
 $3Cl_{2(g)} + I_{2(aq)} \rightarrow 2ICl_{3(s)}$</t>
   </si>
   <si>
-    <t>Vitesse de réaction d'oxydoréduction d'équation suivante : $S_{2}O_{8(aq)}^{2-} + 2I^{-}_{(aq)} \rightarrow 2SO_{4(aq)}^{2-} + I_{2(aq)}$. L'expression de la vitesse de réaction est :</t>
-  </si>
-  <si>
-    <t>La vitesse de réaction à un instant donné :</t>
-  </si>
-  <si>
-    <t>La vitesse de réaction au cours de cette transformation :</t>
-  </si>
-  <si>
-    <t>L'état final d'un système est atteint à un instant $t_f$. La vitesse de réaction pour ce système est maximale :</t>
+    <t>Vitesse de réaction d'oxydoréduction d'équation suivante : $S_{2}O_{8(aq)}^{2-} + 2I^{-}_{(aq)} \rightarrow 2SO_{4(aq)}^{2-} + I_{2(aq)}$. &lt;br&gt;
+L'expression de la vitesse de réaction est :</t>
   </si>
   <si>
     <t>L'urée de formule $(NH_2)_2CO$ se décompose en milieu aqueux et conduit, au cours d'une réaction lente et totale, à la formation d'ion ammonium $NH_4^+$ et cyanate $OCN^-$.
 $(NH_2)_2CO_{(aq)} \rightarrow NH_{4(aq)}^+ + OCN^{-}_{(aq)}$
-L'expression de la vitesse volumique de la réaction est :</t>
-  </si>
-  <si>
-    <t>L'étude cinétique a été réalisée dans un volume V = 100 mL d'une solution d'urée de concentration C = 0,020 mol/L. L'avancement maximal est :</t>
-  </si>
-  <si>
-    <t>L'avancement à la date $t = 3.t_{1/2}$ est :</t>
-  </si>
-  <si>
-    <t>A $t = t_{1/2}$ le taux d'avancement de la réaction est :</t>
-  </si>
-  <si>
-    <t>Iodure de méthyle et hydroxyde de sodium : $CH_3I + HO^- \rightarrow CH_3OH + I^-$. L'évolution de la concentration $C = \frac{C_0}{a + bt}$. A $t = 0$, la valeur de a est égale à :</t>
-  </si>
-  <si>
-    <t>A la fin de la réaction,</t>
-  </si>
-  <si>
-    <t>Le temps de demi-réaction est égal à :</t>
-  </si>
-  <si>
-    <t>La concentration $c'$ du méthanol peut s'écrire :</t>
-  </si>
-  <si>
-    <t>La réaction du dioxyde de soufre : $Zn_{(s)} + 2H_3O^{+}_{(aq)} \rightarrow Zn^{2+}_{(aq)} + H_{2(g)} + 2H_2O_{(l)}$. La variation de pression dans l'erlenmeyer est proportionnelle à la quantité de matière de dihydrogène formé.</t>
-  </si>
-  <si>
-    <t>La quantité de dihydrogène formé est égale :</t>
-  </si>
-  <si>
-    <t>Le volume de gaz dégagé dans l'enceinte est égal à 2,5 L.</t>
-  </si>
-  <si>
-    <t>A la fin de la transformation il reste au fond de l'erlenmeyer :</t>
-  </si>
-  <si>
-    <t>Peroxyde d'hydrogène : Soit l'oxydation en milieu acide du peroxyde d'hydrogène par les ions iodures en excès. On peut exprimer la vitesse volumique de réaction $v$ :</t>
-  </si>
-  <si>
-    <t>La variation temporelle de $[I^{-}_{(aq)}]$ est de la forme (courbe décroissante) :</t>
-  </si>
-  <si>
-    <t>L'oxyde de méthyle $(CH_3)_2O$ gazeux se décompose : $(CH_3)_2O_{(g)} \rightarrow CH_{4(g)} + CO_{(g)} + H_{2(g)}$. La pression initiale $P_0$ peut être calculée par :</t>
-  </si>
-  <si>
-    <t>A l'état final, la pression dans l'enceinte est égale à :</t>
-  </si>
-  <si>
-    <t>L'expression de la pression dans l'enceinte à un instant t est :</t>
-  </si>
-  <si>
-    <t>Au bout de dix secondes, l'avancement est :</t>
-  </si>
-  <si>
-    <t>L'oxydation dans une enceinte fermée, la réaction du dioxyde de soufre $SO_2$ sur le dioxygène $O_2$ donne du trioxyde de soufre $SO_3$.</t>
-  </si>
-  <si>
-    <t>Ion peroxodisulfate et ion iodure : $S_2O_8^{2-} + 2I^- \rightarrow I_2 + 2SO_4^{2-}$. V=100 mL, C1=0.40 mol/L et C2=0.36 mol/L.</t>
-  </si>
-  <si>
-    <t>Etude de la réaction $aA + bB \rightarrow ...$ Au temps $t = 0$, la concentration $c_{0(A)}$ est égale à :</t>
-  </si>
-  <si>
-    <t>Au temps $t_{1/2}$ :</t>
-  </si>
-  <si>
-    <t>Le temps de demi-réaction est compris entre :</t>
-  </si>
-  <si>
-    <t>La courbe 1 correspond au :</t>
-  </si>
-  <si>
-    <t>Si $a = 1$ alors :</t>
-  </si>
-  <si>
-    <t>Si on dilue le mélange réactionnel, les asymptotes horizontales aux courbes 1 et 2 sont plus élevées sur le graphe.</t>
-  </si>
-  <si>
-    <t>$Zn^{2+}_{(aq)} / Zn_{(s)}$ et $H_{3}O^{+}_{(aq)} / H_{2(g)}$</t>
-  </si>
-  <si>
-    <t>$Zn^{2+}_{(aq)} / Zn_{(s)}$ et $H_{3}O^{+}_{(aq)} / H_{2}O_{(l)}$</t>
-  </si>
-  <si>
-    <t>$H_{3}O^{+}_{(aq)} / H_{2(g)}$ et $Zn_{(s)} / Zn^{2+}_{(aq)}$</t>
-  </si>
-  <si>
-    <t>$H_{3}O^{+}_{(aq)} / H_{2}O_{(l)}$ et $Zn_{(s)} / Zn^{2+}_{(aq)}$</t>
-  </si>
-  <si>
-    <t>$H_{2}O_{2(aq)} / O_{2(g)}$ et $H_{2}O_{2(aq)} / H_{2}O_{(l)}$</t>
-  </si>
-  <si>
-    <t>$H_{2}O_{2(aq)} / O_{2(g)}$ et $O_{2(g)} / H_{2}O_{2(aq)}$</t>
-  </si>
-  <si>
-    <t>$O_{2(g)} / H_{2}O_{2(aq)}$ et $H_{2}O_{2(aq)} / H_{2}O_{(l)}$</t>
-  </si>
-  <si>
-    <t>$H_{2}O / H_{2}O_{2(aq)}$ et $O_{2(g)} / H_{2}O_{2(aq)}$</t>
-  </si>
-  <si>
-    <t>$MnO_{4(aq)}^{-} / Mn^{2+}_{(aq)}$ et $Fe^{3+}_{(aq)} / Fe^{2+}_{(aq)}$</t>
-  </si>
-  <si>
-    <t>$MnO_{4(aq)}^{-} / Mn^{2+}_{(aq)}$ et $H^{+}_{(aq)} / H_{2}O_{(l)}$</t>
-  </si>
-  <si>
-    <t>$Mn^{2+}_{(aq)} / MnO_{4(aq)}^{-}$ et $Fe^{2+}_{(aq)} / Fe^{3+}_{(aq)}$</t>
-  </si>
-  <si>
-    <t>Autre réponse</t>
-  </si>
-  <si>
-    <t>$Al_{(s)} / AlO_{2(aq)}^{-}$ et $HO^{-}_{(aq)} / H_{2(g)}$</t>
-  </si>
-  <si>
-    <t>$AlO_{2(aq)}^{-} / Al_{(s)}$ et $HO^{-}_{(aq)} / H_{2(g)}$</t>
-  </si>
-  <si>
-    <t>$AlO_{2(aq)}^{-} / Al_{(s)}$ et $HO^{-}_{(aq)} / H_{2}O_{(l)}$</t>
-  </si>
-  <si>
-    <t>$AlO_{2(aq)}^{-} / Al_{(s)}$ et $H_{2}O_{(l)} / HO^{-}_{(aq)}$</t>
-  </si>
-  <si>
-    <t>$Cl_{2(g)} / Cl^{-}_{(aq)}$ et $HO^{-}_{(aq)} / H_{2}O_{(l)}$</t>
-  </si>
-  <si>
-    <t>$Cl_{2(g)} / Cl^{-}_{(aq)}$ et $H_{2}O_{(l)} / HO^{-}_{(aq)}$</t>
-  </si>
-  <si>
-    <t>$Cl_{2(g)} / Cl^{-}_{(aq)}$ et $Cl_{2(g)} / ClO^{-}_{(aq)}$</t>
-  </si>
-  <si>
-    <t>$Cl_{2(g)} / Cl^{-}_{(aq)}$ et $ClO^{-}_{(aq)} / Cl_{2(g)}$</t>
-  </si>
-  <si>
-    <t>$H_{2}O_{2(aq)} / H_{2}O_{(l)}$ et $I_{2(g)} / I^{-}_{(aq)}$</t>
-  </si>
-  <si>
-    <t>$H_{2}O_{2(aq)} / H_{2}O_{(l)}$ et $I^{-}_{(aq)} / I_{2(g)}$</t>
-  </si>
-  <si>
-    <t>$H_{2}O_{(l)} / H_{2}O_{2(aq)}$ et $I_{2(g)} / I^{-}_{(aq)}$</t>
-  </si>
-  <si>
-    <t>$H_{2}O / H_{2}O_{2(aq)}$ et $I^{-}_{(aq)} / I_{2(g)}$</t>
-  </si>
-  <si>
-    <t>$S_{2}O_{8(aq)}^{2-} / SO_{4(aq)}^{2-}$ et $I^{-}_{(aq)} / I_{2(aq)}$</t>
-  </si>
-  <si>
-    <t>$S_{2}O_{8(aq)}^{2-} / SO_{4(aq)}^{2-}$ et $I_{2(g)} / I^{-}_{(aq)}$</t>
-  </si>
-  <si>
-    <t>$SO_{4(aq)}^{2-} / S_{2}O_{8(aq)}^{2-}$ et $I^{-}_{(aq)} / I_{2(g)}$</t>
-  </si>
-  <si>
-    <t>$SO_{4(aq)}^{2-} / S_{2}O_{8(aq)}^{2-}$ et $I_{2(g)} / I^{-}_{(aq)}$</t>
-  </si>
-  <si>
-    <t>$Cl_{2(g)} / Cl^{-}_{(aq)}$ et $I_{2(g)} / I^{-}_{(aq)}$</t>
-  </si>
-  <si>
-    <t>$Cl^{-}_{(aq)} / Cl_{2(g)}$ et $I^{-}_{(aq)} / I_{2(g)}$</t>
-  </si>
-  <si>
-    <t>$Cl_{2(g)} / Cl^{-}_{(aq)}$ et $ICl_{3(s)} / I_{2(g)}$</t>
-  </si>
-  <si>
-    <t>$Cl_{2(g)} / Cl^{-}_{(aq)}$ et $I_{2(g)} / ICl_{3(s)}$</t>
-  </si>
-  <si>
-    <t>$V = \frac{1}{2}\frac{d[I_2]}{dt}$</t>
-  </si>
-  <si>
-    <t>$V = - \frac{d[I_2]}{dt}$</t>
-  </si>
-  <si>
-    <t>$V = \frac{d[I_2]}{dt}$</t>
-  </si>
-  <si>
-    <t>$V = \frac{1}{V_1 + V_2}\frac{d[I_2]}{dt}$</t>
-  </si>
-  <si>
-    <t>Dépend de la couleur des espèces chimiques qui constituent le système</t>
-  </si>
-  <si>
-    <t>Dépend du volume du mélange réactionnel</t>
-  </si>
-  <si>
-    <t>Dépend de la concentration des produits</t>
-  </si>
-  <si>
-    <t>Dépend de la température</t>
-  </si>
-  <si>
-    <t>Augmente avec le temps</t>
-  </si>
-  <si>
-    <t>Diminue avec le temps</t>
-  </si>
-  <si>
-    <t>Augmente puis diminue</t>
-  </si>
-  <si>
-    <t>Ne varie pas</t>
-  </si>
-  <si>
-    <t>à l'instant $t_f$</t>
-  </si>
-  <si>
-    <t>à l'instant $t = 0$</t>
-  </si>
-  <si>
-    <t>à l'instant $t_{1/2}$</t>
-  </si>
-  <si>
-    <t>à l'instant $t = \infty$</t>
-  </si>
-  <si>
-    <t>$v = \frac{d[(NH_2)_2CO]}{dt}$</t>
-  </si>
-  <si>
-    <t>$v = -\frac{d[(NH_2)_2CO]}{dt}$</t>
-  </si>
-  <si>
-    <t>$v = \frac{1}{V}\frac{d[(NH_2)_2CO]}{dt}$</t>
-  </si>
-  <si>
-    <t>$v = -\frac{1}{V}\frac{d[(NH_2)_2CO]}{dt}$</t>
-  </si>
-  <si>
-    <t>$x_{max} = 1,0~mmol$</t>
-  </si>
-  <si>
-    <t>$x_{max} = 1,7~mmol$</t>
-  </si>
-  <si>
-    <t>$x_{max} = 2,0~mmol$</t>
-  </si>
-  <si>
-    <t>$x_{max} = 4,0~mmol$</t>
-  </si>
-  <si>
-    <t>$x(3t_{1/2}) = 1,35~mmol$</t>
-  </si>
-  <si>
-    <t>$x(3t_{1/2}) = 1,55~mmol$</t>
-  </si>
-  <si>
-    <t>$x(3t_{1/2}) = 1,75~mmol$</t>
-  </si>
-  <si>
-    <t>$x(3t_{1/2}) = 2,0~mmol$</t>
-  </si>
-  <si>
-    <t>40%</t>
-  </si>
-  <si>
-    <t>50%</t>
-  </si>
-  <si>
-    <t>60%</t>
-  </si>
-  <si>
-    <t>80%</t>
-  </si>
-  <si>
-    <t>$a = 0$</t>
-  </si>
-  <si>
-    <t>$a = 1$</t>
-  </si>
-  <si>
-    <t>$a = -1$</t>
-  </si>
-  <si>
-    <t>il reste encore d'iodure de méthyle dans le milieu réactionnel.</t>
-  </si>
-  <si>
-    <t>il ne reste plus d'iodure de méthyle dans le milieu réactionnel.</t>
-  </si>
-  <si>
-    <t>l'iodure de méthyle est une espèce spectatrice.</t>
-  </si>
-  <si>
-    <t>$t_{1/2} = a$</t>
-  </si>
-  <si>
-    <t>$t_{1/2} = b$</t>
-  </si>
-  <si>
-    <t>$t_{1/2} = 1/b$</t>
-  </si>
-  <si>
-    <t>$t_{1/2} = -b$</t>
-  </si>
-  <si>
-    <t>$c' = c_0 \frac{bt}{1 - bt}$</t>
-  </si>
-  <si>
-    <t>$c' = c_0 \frac{1 + bt}{bt}$</t>
-  </si>
-  <si>
-    <t>$c' = c_0 \frac{bt}{1 + bt}$</t>
-  </si>
-  <si>
-    <t>$c' = c_0 \frac{1 - bt}{bt}$</t>
-  </si>
-  <si>
-    <t>Vrai</t>
-  </si>
-  <si>
-    <t>Faux</t>
-  </si>
-  <si>
-    <t>$n(H_2) = 0,05~mol$</t>
-  </si>
-  <si>
-    <t>$n(H_2) = 0,06~mol$</t>
-  </si>
-  <si>
-    <t>$n(H_2) = 0,08~mol$</t>
-  </si>
-  <si>
-    <t>$n(H_2) = 0,1~mol$</t>
-  </si>
-  <si>
-    <t>$V = 2,5~L$</t>
-  </si>
-  <si>
-    <t>$V = 4~L$</t>
-  </si>
-  <si>
-    <t>$V = 5~L$</t>
-  </si>
-  <si>
-    <t>$V = 8~L$</t>
-  </si>
-  <si>
-    <t>moins de la moitié de la quantité de matière initiale de zinc.</t>
-  </si>
-  <si>
-    <t>la moitié de la quantité de matière initiale de zinc.</t>
-  </si>
-  <si>
-    <t>plus de la moitié de la quantité de matière initiale de zinc.</t>
-  </si>
-  <si>
-    <t>Le zinc est en défaut.</t>
-  </si>
-  <si>
-    <t>Comme la dérivée temporelle de l'avancement x.</t>
-  </si>
-  <si>
-    <t>Comme la dérivée volumique de l'avancement x.</t>
-  </si>
-  <si>
-    <t>En divisant la pente de la tangente à l'origine de la courbe $x(t)$ par le volume.</t>
-  </si>
-  <si>
-    <t>$P_0$</t>
-  </si>
-  <si>
-    <t>$2P_0$</t>
-  </si>
-  <si>
-    <t>$3P_0$</t>
-  </si>
-  <si>
-    <t>Autre</t>
-  </si>
-  <si>
-    <t>$4P_0$</t>
-  </si>
-  <si>
-    <t>$P = P_0 + \frac{x(t)RT}{V}$</t>
-  </si>
-  <si>
-    <t>$P = P_0 + \frac{2x(t)RT}{V}$</t>
-  </si>
-  <si>
-    <t>$P = P_0 + \frac{3x(t)RT}{V}$</t>
-  </si>
-  <si>
-    <t>$P = P_0 + \frac{4x(t)RT}{V}$</t>
-  </si>
-  <si>
-    <t>$x = 0,0125~mol$</t>
-  </si>
-  <si>
-    <t>$x = 0,125~mol$</t>
-  </si>
-  <si>
-    <t>$x = 1,25~mol$</t>
-  </si>
-  <si>
-    <t>Le mélange est réalisé dans des conditions stœchiométriques.</t>
-  </si>
-  <si>
-    <t>La quantité maximale de trioxyde de soufre formé est 20 mmol.</t>
-  </si>
-  <si>
-    <t>Le temps de demi-réaction est $t_{1/2} = 30~s$.</t>
-  </si>
-  <si>
-    <t>La courbe 3 représente l'évolution de la quantité de dioxygène au cours du temps.</t>
-  </si>
-  <si>
-    <t>Le réactif limitant est l'ion iodure.</t>
-  </si>
-  <si>
-    <t>La réaction est finie à $t &gt; 50~min$.</t>
-  </si>
-  <si>
-    <t>La vitesse volumique molaire est proportionnelle au volume.</t>
-  </si>
-  <si>
-    <t>Cette vitesse est d'abord positive, s'annule puis est négative.</t>
-  </si>
-  <si>
-    <t>$\frac{C_0}{5}$</t>
-  </si>
-  <si>
-    <t>$\frac{4C_0}{5}$</t>
-  </si>
-  <si>
-    <t>$\frac{C_{0(B)}}{4}$</t>
-  </si>
-  <si>
-    <t>$\frac{4C_{0(B)}}{5}$</t>
-  </si>
-  <si>
-    <t>50% d'un des réactifs a disparu.</t>
-  </si>
-  <si>
-    <t>25% d'un des réactifs a disparu.</t>
-  </si>
-  <si>
-    <t>75% d'un des réactifs a disparu.</t>
-  </si>
-  <si>
-    <t>2 et 3 heures.</t>
-  </si>
-  <si>
-    <t>3 et 4 heures.</t>
-  </si>
-  <si>
-    <t>4 et 5 heures.</t>
-  </si>
-  <si>
-    <t>5 et 6 heures.</t>
-  </si>
-  <si>
-    <t>réactif A.</t>
-  </si>
-  <si>
-    <t>réactif B.</t>
-  </si>
-  <si>
-    <t>$b = 0$</t>
-  </si>
-  <si>
-    <t>$b = a$</t>
-  </si>
-  <si>
-    <t>$b = 2a$</t>
-  </si>
-  <si>
-    <t>$b = 8a$</t>
-  </si>
-  <si>
-    <t>CHIMIE CINETIQUE</t>
+&lt;br&gt;L'expression de la vitesse volumique de la réaction est :</t>
+  </si>
+  <si>
+    <t>Iodure de méthyle et hydroxyde de sodium : $CH_3I + HO^- \rightarrow CH_3OH + I^-$. 
+L'évolution de la concentration $C = \frac{C_0}{a + bt}$. A $t = 0$, 
+&lt;br&gt;la valeur de a est égale à :</t>
+  </si>
+  <si>
+    <t>La réaction du dioxyde de soufre : $Zn_{(s)} + 2H_3O^{+}_{(aq)} \rightarrow Zn^{2+}_{(aq)} + H_{2(g)} + 2H_2O_{(l)}$. 
+&lt;br&gt;La variation de pression dans l'erlenmeyer est proportionnelle à la quantité de matière de dihydrogène formé.</t>
+  </si>
+  <si>
+    <t>L'oxyde de méthyle $(CH_3)_2O$ gazeux se décompose : $(CH_3)_2O_{(g)} \rightarrow CH_{4(g)} + CO_{(g)} + H_{2(g)}$. 
+&lt;br&gt;La pression initiale $P_0$ peut être calculée par :</t>
   </si>
 </sst>
 </file>
@@ -1119,10 +1124,10 @@
         <v>4</v>
       </c>
       <c r="E1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>5</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>6</v>
       </c>
       <c r="G1" s="2" t="s">
         <v>7</v>
@@ -1142,25 +1147,25 @@
     </row>
     <row r="2" spans="1:11" ht="181.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>182</v>
+        <v>169</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>12</v>
+        <v>170</v>
       </c>
       <c r="C2" s="9" t="s">
         <v>3</v>
       </c>
       <c r="D2" s="15" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="E2" s="15" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="F2" s="15" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="G2" s="15" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="H2" s="8"/>
       <c r="I2" s="10"/>
@@ -1170,22 +1175,22 @@
     <row r="3" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A3" s="11"/>
       <c r="B3" s="15" t="s">
-        <v>13</v>
+        <v>171</v>
       </c>
       <c r="C3" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="G3" s="15" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="H3" s="12"/>
       <c r="I3" s="14"/>
@@ -1195,22 +1200,22 @@
     <row r="4" spans="1:11" ht="75" x14ac:dyDescent="0.25">
       <c r="A4" s="11"/>
       <c r="B4" s="15" t="s">
-        <v>14</v>
+        <v>172</v>
       </c>
       <c r="C4" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="F4" s="15" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="G4" s="15" t="s">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="H4" s="12"/>
       <c r="I4" s="14"/>
@@ -1220,22 +1225,22 @@
     <row r="5" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A5" s="11"/>
       <c r="B5" s="15" t="s">
-        <v>15</v>
+        <v>173</v>
       </c>
       <c r="C5" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D5" s="15" t="s">
-        <v>62</v>
+        <v>49</v>
       </c>
       <c r="E5" s="15" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="F5" s="15" t="s">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="G5" s="15" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="H5" s="12"/>
       <c r="I5" s="14"/>
@@ -1245,22 +1250,22 @@
     <row r="6" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A6" s="11"/>
       <c r="B6" s="15" t="s">
-        <v>16</v>
+        <v>174</v>
       </c>
       <c r="C6" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D6" s="15" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="E6" s="15" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="F6" s="15" t="s">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="G6" s="15" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="H6" s="12"/>
       <c r="I6" s="14"/>
@@ -1270,22 +1275,22 @@
     <row r="7" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A7" s="11"/>
       <c r="B7" s="15" t="s">
-        <v>17</v>
+        <v>175</v>
       </c>
       <c r="C7" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="F7" s="15" t="s">
-        <v>72</v>
+        <v>58</v>
       </c>
       <c r="G7" s="15" t="s">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="H7" s="12"/>
       <c r="I7" s="14"/>
@@ -1295,22 +1300,22 @@
     <row r="8" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A8" s="11"/>
       <c r="B8" s="15" t="s">
-        <v>18</v>
+        <v>176</v>
       </c>
       <c r="C8" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="15" t="s">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="F8" s="15" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
       <c r="G8" s="15" t="s">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="H8" s="12"/>
       <c r="I8" s="14"/>
@@ -1320,22 +1325,22 @@
     <row r="9" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A9" s="11"/>
       <c r="B9" s="15" t="s">
-        <v>19</v>
+        <v>177</v>
       </c>
       <c r="C9" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="F9" s="15" t="s">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="G9" s="15" t="s">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="H9" s="12"/>
       <c r="I9" s="14"/>
@@ -1345,22 +1350,22 @@
     <row r="10" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A10" s="11"/>
       <c r="B10" s="15" t="s">
-        <v>20</v>
+        <v>178</v>
       </c>
       <c r="C10" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D10" s="15" t="s">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="E10" s="15" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="F10" s="15" t="s">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="G10" s="15" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="H10" s="12"/>
       <c r="I10" s="14"/>
@@ -1370,22 +1375,22 @@
     <row r="11" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="11"/>
       <c r="B11" s="15" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="C11" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="E11" s="15" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="F11" s="15" t="s">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="G11" s="15" t="s">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="H11" s="12"/>
       <c r="I11" s="14"/>
@@ -1395,22 +1400,22 @@
     <row r="12" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" s="11"/>
       <c r="B12" s="15" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="C12" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D12" s="15" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="E12" s="15" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="F12" s="15" t="s">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="G12" s="15" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="H12" s="12"/>
       <c r="I12" s="14"/>
@@ -1420,22 +1425,22 @@
     <row r="13" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="11"/>
       <c r="B13" s="15" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="C13" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D13" s="15" t="s">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="E13" s="15" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="F13" s="15" t="s">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="G13" s="15" t="s">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="H13" s="12"/>
       <c r="I13" s="14"/>
@@ -1445,22 +1450,22 @@
     <row r="14" spans="1:11" ht="120" x14ac:dyDescent="0.25">
       <c r="A14" s="11"/>
       <c r="B14" s="15" t="s">
-        <v>24</v>
+        <v>179</v>
       </c>
       <c r="C14" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D14" s="15" t="s">
-        <v>98</v>
+        <v>85</v>
       </c>
       <c r="E14" s="15" t="s">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="F14" s="15" t="s">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="G14" s="15" t="s">
-        <v>101</v>
+        <v>88</v>
       </c>
       <c r="H14" s="12"/>
       <c r="I14" s="14"/>
@@ -1470,22 +1475,22 @@
     <row r="15" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A15" s="11"/>
       <c r="B15" s="15" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="C15" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D15" s="15" t="s">
-        <v>102</v>
+        <v>89</v>
       </c>
       <c r="E15" s="15" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="F15" s="15" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="G15" s="15" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="H15" s="12"/>
       <c r="I15" s="14"/>
@@ -1495,22 +1500,22 @@
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="11"/>
       <c r="B16" s="15" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="C16" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D16" s="15" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="E16" s="15" t="s">
-        <v>107</v>
+        <v>95</v>
       </c>
       <c r="F16" s="15" t="s">
-        <v>108</v>
+        <v>94</v>
       </c>
       <c r="G16" s="15" t="s">
-        <v>109</v>
+        <v>96</v>
       </c>
       <c r="H16" s="12"/>
       <c r="I16" s="14"/>
@@ -1520,45 +1525,45 @@
     <row r="17" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="11"/>
       <c r="B17" s="15" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="C17" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D17" s="15" t="s">
-        <v>110</v>
+        <v>97</v>
       </c>
       <c r="E17" s="15" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="F17" s="15" t="s">
-        <v>112</v>
+        <v>98</v>
       </c>
       <c r="G17" s="15" t="s">
-        <v>113</v>
+        <v>100</v>
       </c>
       <c r="H17" s="12"/>
       <c r="I17" s="14"/>
     </row>
-    <row r="18" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" ht="75" x14ac:dyDescent="0.25">
       <c r="A18" s="11"/>
       <c r="B18" s="15" t="s">
-        <v>28</v>
+        <v>180</v>
       </c>
       <c r="C18" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D18" s="15" t="s">
-        <v>114</v>
+        <v>101</v>
       </c>
       <c r="E18" s="15" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="F18" s="15" t="s">
-        <v>116</v>
+        <v>102</v>
       </c>
       <c r="G18" s="15" t="s">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="H18" s="12"/>
       <c r="I18" s="14"/>
@@ -1566,22 +1571,22 @@
     <row r="19" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A19" s="11"/>
       <c r="B19" s="15" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="C19" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D19" s="15" t="s">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="E19" s="15" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="F19" s="15" t="s">
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="G19" s="15" t="s">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="H19" s="12"/>
       <c r="I19" s="14"/>
@@ -1589,22 +1594,22 @@
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="11"/>
       <c r="B20" s="15" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="C20" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D20" s="15" t="s">
-        <v>120</v>
+        <v>107</v>
       </c>
       <c r="E20" s="15" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="F20" s="15" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="G20" s="15" t="s">
-        <v>123</v>
+        <v>110</v>
       </c>
       <c r="H20" s="12"/>
       <c r="I20" s="14"/>
@@ -1612,41 +1617,41 @@
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="11"/>
       <c r="B21" s="15" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="C21" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D21" s="15" t="s">
-        <v>124</v>
+        <v>111</v>
       </c>
       <c r="E21" s="15" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="F21" s="15" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="G21" s="15" t="s">
-        <v>127</v>
+        <v>114</v>
       </c>
       <c r="H21" s="12"/>
       <c r="I21" s="14"/>
     </row>
-    <row r="22" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" ht="90" x14ac:dyDescent="0.25">
       <c r="A22" s="11"/>
       <c r="B22" s="15" t="s">
-        <v>32</v>
+        <v>181</v>
       </c>
       <c r="C22" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D22" s="15" t="s">
-        <v>128</v>
-      </c>
-      <c r="E22" s="15" t="s">
-        <v>129</v>
-      </c>
-      <c r="F22" s="15"/>
+        <v>115</v>
+      </c>
+      <c r="E22" s="15"/>
+      <c r="F22" s="15" t="s">
+        <v>116</v>
+      </c>
       <c r="G22" s="15"/>
       <c r="H22" s="12"/>
       <c r="I22" s="14"/>
@@ -1654,22 +1659,22 @@
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="11"/>
       <c r="B23" s="15" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="C23" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D23" s="15" t="s">
-        <v>130</v>
+        <v>117</v>
       </c>
       <c r="E23" s="15" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="F23" s="15" t="s">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="G23" s="15" t="s">
-        <v>133</v>
+        <v>120</v>
       </c>
       <c r="H23" s="12"/>
       <c r="I23" s="14"/>
@@ -1677,22 +1682,22 @@
     <row r="24" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A24" s="11"/>
       <c r="B24" s="15" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="C24" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D24" s="15" t="s">
-        <v>134</v>
+        <v>121</v>
       </c>
       <c r="E24" s="15" t="s">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="F24" s="15" t="s">
-        <v>136</v>
+        <v>122</v>
       </c>
       <c r="G24" s="15" t="s">
-        <v>137</v>
+        <v>124</v>
       </c>
       <c r="H24" s="12"/>
       <c r="I24" s="14"/>
@@ -1700,22 +1705,22 @@
     <row r="25" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A25" s="11"/>
       <c r="B25" s="15" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C25" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D25" s="15" t="s">
-        <v>138</v>
+        <v>125</v>
       </c>
       <c r="E25" s="15" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="F25" s="15" t="s">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="G25" s="15" t="s">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="H25" s="12"/>
       <c r="I25" s="14"/>
@@ -1723,22 +1728,22 @@
     <row r="26" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A26" s="11"/>
       <c r="B26" s="15" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="C26" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D26" s="15" t="s">
-        <v>142</v>
+        <v>129</v>
       </c>
       <c r="E26" s="15" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="F26" s="15" t="s">
-        <v>144</v>
+        <v>130</v>
       </c>
       <c r="G26" s="15" t="s">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="H26" s="12"/>
       <c r="I26" s="14"/>
@@ -1746,18 +1751,18 @@
     <row r="27" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A27" s="11"/>
       <c r="B27" s="15" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="C27" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D27" s="15" t="s">
-        <v>128</v>
-      </c>
-      <c r="E27" s="15" t="s">
-        <v>129</v>
-      </c>
-      <c r="F27" s="15"/>
+        <v>115</v>
+      </c>
+      <c r="E27" s="15"/>
+      <c r="F27" s="15" t="s">
+        <v>116</v>
+      </c>
       <c r="G27" s="15"/>
       <c r="H27" s="12"/>
       <c r="I27" s="14"/>
@@ -1765,22 +1770,22 @@
     <row r="28" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A28" s="11"/>
       <c r="B28" s="15" t="s">
-        <v>38</v>
+        <v>182</v>
       </c>
       <c r="C28" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D28" s="15" t="s">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="E28" s="15" t="s">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="F28" s="15" t="s">
-        <v>147</v>
+        <v>133</v>
       </c>
       <c r="G28" s="15" t="s">
-        <v>148</v>
+        <v>135</v>
       </c>
       <c r="H28" s="12"/>
       <c r="I28" s="14"/>
@@ -1788,22 +1793,22 @@
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="11"/>
       <c r="B29" s="15" t="s">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="C29" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D29" s="15" t="s">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="E29" s="15" t="s">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="F29" s="15" t="s">
-        <v>147</v>
+        <v>133</v>
       </c>
       <c r="G29" s="15" t="s">
-        <v>149</v>
+        <v>136</v>
       </c>
       <c r="H29" s="12"/>
       <c r="I29" s="14"/>
@@ -1811,22 +1816,22 @@
     <row r="30" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A30" s="11"/>
       <c r="B30" s="15" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="C30" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D30" s="15" t="s">
-        <v>150</v>
+        <v>137</v>
       </c>
       <c r="E30" s="15" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="F30" s="15" t="s">
-        <v>152</v>
+        <v>138</v>
       </c>
       <c r="G30" s="15" t="s">
-        <v>153</v>
+        <v>140</v>
       </c>
       <c r="H30" s="12"/>
       <c r="I30" s="14"/>
@@ -1834,22 +1839,22 @@
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="11"/>
       <c r="B31" s="15" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="C31" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D31" s="15" t="s">
-        <v>154</v>
+        <v>141</v>
       </c>
       <c r="E31" s="15" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="F31" s="15" t="s">
-        <v>156</v>
+        <v>142</v>
       </c>
       <c r="G31" s="15" t="s">
-        <v>148</v>
+        <v>135</v>
       </c>
       <c r="H31" s="12"/>
       <c r="I31" s="14"/>
@@ -1857,22 +1862,22 @@
     <row r="32" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A32" s="11"/>
       <c r="B32" s="15" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="C32" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D32" s="15" t="s">
-        <v>157</v>
+        <v>144</v>
       </c>
       <c r="E32" s="15" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
       <c r="F32" s="15" t="s">
-        <v>159</v>
+        <v>145</v>
       </c>
       <c r="G32" s="15" t="s">
-        <v>160</v>
+        <v>147</v>
       </c>
       <c r="H32" s="12"/>
       <c r="I32" s="14"/>
@@ -1880,22 +1885,22 @@
     <row r="33" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A33" s="11"/>
       <c r="B33" s="15" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="C33" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D33" s="15" t="s">
-        <v>161</v>
+        <v>148</v>
       </c>
       <c r="E33" s="15" t="s">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="F33" s="15" t="s">
-        <v>163</v>
+        <v>149</v>
       </c>
       <c r="G33" s="15" t="s">
-        <v>164</v>
+        <v>151</v>
       </c>
       <c r="H33" s="12"/>
       <c r="I33" s="14"/>
@@ -1903,22 +1908,22 @@
     <row r="34" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A34" s="11"/>
       <c r="B34" s="15" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="C34" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D34" s="15" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="E34" s="15" t="s">
-        <v>166</v>
+        <v>154</v>
       </c>
       <c r="F34" s="15" t="s">
-        <v>167</v>
+        <v>153</v>
       </c>
       <c r="G34" s="15" t="s">
-        <v>168</v>
+        <v>155</v>
       </c>
       <c r="H34" s="12"/>
       <c r="I34" s="14"/>
@@ -1926,22 +1931,22 @@
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" s="11"/>
       <c r="B35" s="15" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="C35" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D35" s="15" t="s">
-        <v>169</v>
+        <v>156</v>
       </c>
       <c r="E35" s="15" t="s">
-        <v>170</v>
+        <v>158</v>
       </c>
       <c r="F35" s="15" t="s">
-        <v>171</v>
+        <v>157</v>
       </c>
       <c r="G35" s="15" t="s">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="H35" s="12"/>
       <c r="I35" s="14"/>
@@ -1949,22 +1954,22 @@
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" s="11"/>
       <c r="B36" s="15" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="C36" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D36" s="15" t="s">
-        <v>172</v>
+        <v>159</v>
       </c>
       <c r="E36" s="15" t="s">
-        <v>173</v>
+        <v>161</v>
       </c>
       <c r="F36" s="15" t="s">
-        <v>174</v>
+        <v>160</v>
       </c>
       <c r="G36" s="15" t="s">
-        <v>175</v>
+        <v>162</v>
       </c>
       <c r="H36" s="12"/>
       <c r="I36" s="14"/>
@@ -1972,19 +1977,19 @@
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" s="11"/>
       <c r="B37" s="15" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="C37" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D37" s="15" t="s">
-        <v>176</v>
+        <v>163</v>
       </c>
       <c r="E37" s="15" t="s">
-        <v>177</v>
+        <v>48</v>
       </c>
       <c r="F37" s="15" t="s">
-        <v>61</v>
+        <v>164</v>
       </c>
       <c r="G37" s="15"/>
       <c r="H37" s="12"/>
@@ -1993,22 +1998,22 @@
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" s="11"/>
       <c r="B38" s="15" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="C38" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D38" s="15" t="s">
-        <v>178</v>
+        <v>165</v>
       </c>
       <c r="E38" s="15" t="s">
-        <v>179</v>
+        <v>167</v>
       </c>
       <c r="F38" s="15" t="s">
-        <v>180</v>
+        <v>166</v>
       </c>
       <c r="G38" s="15" t="s">
-        <v>181</v>
+        <v>168</v>
       </c>
       <c r="H38" s="12"/>
       <c r="I38" s="14"/>
@@ -2016,18 +2021,18 @@
     <row r="39" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A39" s="11"/>
       <c r="B39" s="15" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="C39" s="13" t="s">
         <v>3</v>
       </c>
       <c r="D39" s="15" t="s">
-        <v>128</v>
-      </c>
-      <c r="E39" s="15" t="s">
-        <v>129</v>
-      </c>
-      <c r="F39" s="15"/>
+        <v>115</v>
+      </c>
+      <c r="E39" s="15"/>
+      <c r="F39" s="15" t="s">
+        <v>116</v>
+      </c>
       <c r="G39" s="15"/>
       <c r="H39" s="12"/>
       <c r="I39" s="14"/>
